--- a/BOM/Petal_Bionic_Butterfly_BOM(2nd).xlsx
+++ b/BOM/Petal_Bionic_Butterfly_BOM(2nd).xlsx
@@ -32,7 +32,7 @@
     <t>PETAL - A BIONIC BUTTERFLY (BOM)</t>
   </si>
   <si>
-    <t>DATE - 25-09-2026</t>
+    <t>DATE - 08-10-2026</t>
   </si>
   <si>
     <t>AUTHOR: RYTHM RAJ (@rythmmm on pixl)</t>
